--- a/Excel.xlsx
+++ b/Excel.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30326"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30430"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\emilg\Desktop\INZYNIERKA\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{485444E9-0D39-44CD-9367-D7F3670875EE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B2465E2-DAE7-4640-A1D4-A81580179B87}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -18,7 +18,7 @@
   </sheets>
   <definedNames>
     <definedName name="ExternalData_1" localSheetId="0" hidden="1">Plan_pracy!#REF!</definedName>
-    <definedName name="ExternalData_2" localSheetId="0" hidden="1">Plan_pracy!$A$3:$E$98</definedName>
+    <definedName name="ExternalData_2" localSheetId="0" hidden="1">Plan_pracy!$A$3:$E$94</definedName>
   </definedNames>
   <calcPr calcId="191029"/>
   <extLst>
@@ -58,7 +58,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="254">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="434" uniqueCount="255">
   <si>
     <t>Analizy trendów</t>
   </si>
@@ -867,6 +867,9 @@
   </si>
   <si>
     <t>Wykonano</t>
+  </si>
+  <si>
+    <t>Pokazac wzrastajace zapotrzebowanie na  tego typu sprzet</t>
   </si>
 </sst>
 </file>
@@ -934,7 +937,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="7">
+  <fills count="8">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -969,6 +972,12 @@
       <patternFill patternType="solid">
         <fgColor rgb="FF70AD47"/>
         <bgColor theme="9"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0"/>
+        <bgColor theme="9" tint="0.79998168889431442"/>
       </patternFill>
     </fill>
   </fills>
@@ -1010,7 +1019,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1054,15 +1063,8 @@
     <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="3" borderId="2" xfId="0" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="4" fillId="6" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="10" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
@@ -1073,25 +1075,23 @@
     <xf numFmtId="0" fontId="7" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="5" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="10" fontId="6" fillId="5" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="14" fontId="0" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="7" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <dxfs count="6">
-    <dxf>
-      <font>
-        <strike val="0"/>
-        <outline val="0"/>
-        <shadow val="0"/>
-        <u val="none"/>
-        <vertAlign val="baseline"/>
-        <sz val="14"/>
-        <name val="Calibri"/>
-        <family val="2"/>
-        <scheme val="minor"/>
-      </font>
-      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
-    </dxf>
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
     </dxf>
@@ -1108,6 +1108,20 @@
     <dxf>
       <numFmt numFmtId="0" formatCode="General"/>
       <alignment horizontal="left" vertical="center" textRotation="0" wrapText="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
+    </dxf>
+    <dxf>
+      <font>
+        <strike val="0"/>
+        <outline val="0"/>
+        <shadow val="0"/>
+        <u val="none"/>
+        <vertAlign val="baseline"/>
+        <sz val="14"/>
+        <name val="Calibri"/>
+        <family val="2"/>
+        <scheme val="minor"/>
+      </font>
+      <alignment horizontal="center" vertical="center" textRotation="0" indent="0" justifyLastLine="0" shrinkToFit="0" readingOrder="0"/>
     </dxf>
   </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1145,14 +1159,14 @@
 </file>
 
 <file path=xl/tables/table1.xml><?xml version="1.0" encoding="utf-8"?>
-<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{72505675-E1F4-4723-84FB-9DF90E2DB6DF}" name="Numer_Tytuł_Opis_i_zakres_prac5" displayName="Numer_Tytuł_Opis_i_zakres_prac5" ref="A3:E98" tableType="queryTable" totalsRowShown="0" headerRowDxfId="0">
-  <autoFilter ref="A3:E98" xr:uid="{72505675-E1F4-4723-84FB-9DF90E2DB6DF}"/>
+<table xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="xr xr3" id="4" xr:uid="{72505675-E1F4-4723-84FB-9DF90E2DB6DF}" name="Numer_Tytuł_Opis_i_zakres_prac5" displayName="Numer_Tytuł_Opis_i_zakres_prac5" ref="A3:E94" tableType="queryTable" totalsRowShown="0" headerRowDxfId="5">
+  <autoFilter ref="A3:E94" xr:uid="{72505675-E1F4-4723-84FB-9DF90E2DB6DF}"/>
   <tableColumns count="5">
-    <tableColumn id="1" xr3:uid="{AB939AD1-8CF3-46C0-B193-8E4A9894E131}" uniqueName="1" name="Rodział" queryTableFieldId="1" dataDxfId="5"/>
-    <tableColumn id="8" xr3:uid="{E170CD49-73B5-400D-92B9-6807F7914FDF}" uniqueName="8" name="Podrozdziały" queryTableFieldId="8" dataDxfId="4"/>
-    <tableColumn id="4" xr3:uid="{C5A1867C-7B0F-4EBC-AB3D-39DF167D145F}" uniqueName="4" name="Terim wysłania" queryTableFieldId="4" dataDxfId="3"/>
-    <tableColumn id="15" xr3:uid="{5CA424E4-EBCF-49BB-813E-E6E5EFD8F2E7}" uniqueName="15" name="Status" queryTableFieldId="9" dataDxfId="2"/>
-    <tableColumn id="3" xr3:uid="{F651BAD9-937A-4833-AF1F-444559983DFF}" uniqueName="3" name="Opis i zakres prac" queryTableFieldId="3" dataDxfId="1"/>
+    <tableColumn id="1" xr3:uid="{AB939AD1-8CF3-46C0-B193-8E4A9894E131}" uniqueName="1" name="Rodział" queryTableFieldId="1" dataDxfId="4"/>
+    <tableColumn id="8" xr3:uid="{E170CD49-73B5-400D-92B9-6807F7914FDF}" uniqueName="8" name="Podrozdziały" queryTableFieldId="8" dataDxfId="3"/>
+    <tableColumn id="4" xr3:uid="{C5A1867C-7B0F-4EBC-AB3D-39DF167D145F}" uniqueName="4" name="Terim wysłania" queryTableFieldId="4" dataDxfId="2"/>
+    <tableColumn id="15" xr3:uid="{5CA424E4-EBCF-49BB-813E-E6E5EFD8F2E7}" uniqueName="15" name="Status" queryTableFieldId="9" dataDxfId="1"/>
+    <tableColumn id="3" xr3:uid="{F651BAD9-937A-4833-AF1F-444559983DFF}" uniqueName="3" name="Opis i zakres prac" queryTableFieldId="3" dataDxfId="0"/>
   </tableColumns>
   <tableStyleInfo name="TableStyleMedium7" showFirstColumn="0" showLastColumn="0" showRowStripes="1" showColumnStripes="0"/>
 </table>
@@ -1421,7 +1435,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{C4B02167-341C-43F0-A11C-74859C44C3D3}">
-  <dimension ref="A1:E98"/>
+  <dimension ref="A1:E94"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="34.1796875" style="2" customWidth="1"/>
@@ -1432,40 +1446,40 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:5" ht="41.5" customHeight="1" x14ac:dyDescent="0.35">
-      <c r="A1" s="18" t="s">
+      <c r="A1" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="B1" s="18"/>
-      <c r="C1" s="18"/>
-      <c r="D1" s="18"/>
-      <c r="E1" s="18"/>
+      <c r="B1" s="21"/>
+      <c r="C1" s="21"/>
+      <c r="D1" s="21"/>
+      <c r="E1" s="21"/>
     </row>
     <row r="2" spans="1:5" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A2" s="19" t="s">
+      <c r="A2" s="17" t="s">
         <v>240</v>
       </c>
-      <c r="B2" s="20">
+      <c r="B2" s="22">
         <f>COUNTA(Numer_Tytuł_Opis_i_zakres_prac5[Status])/COUNTA(Numer_Tytuł_Opis_i_zakres_prac5[Rodział])</f>
-        <v>1.0526315789473684E-2</v>
-      </c>
-      <c r="C2" s="20"/>
-      <c r="D2" s="20"/>
-      <c r="E2" s="20"/>
+        <v>8.7912087912087919E-2</v>
+      </c>
+      <c r="C2" s="22"/>
+      <c r="D2" s="22"/>
+      <c r="E2" s="22"/>
     </row>
     <row r="3" spans="1:5" s="1" customFormat="1" ht="18.5" x14ac:dyDescent="0.35">
-      <c r="A3" s="21" t="s">
+      <c r="A3" s="18" t="s">
         <v>242</v>
       </c>
-      <c r="B3" s="21" t="s">
+      <c r="B3" s="18" t="s">
         <v>243</v>
       </c>
-      <c r="C3" s="22" t="s">
+      <c r="C3" s="19" t="s">
         <v>233</v>
       </c>
-      <c r="D3" s="23" t="s">
+      <c r="D3" s="20" t="s">
         <v>252</v>
       </c>
-      <c r="E3" s="23" t="s">
+      <c r="E3" s="20" t="s">
         <v>232</v>
       </c>
     </row>
@@ -1475,9 +1489,7 @@
       </c>
       <c r="B4" s="9"/>
       <c r="C4" s="10"/>
-      <c r="D4" s="10" t="s">
-        <v>253</v>
-      </c>
+      <c r="D4" s="10"/>
       <c r="E4" s="11"/>
     </row>
     <row r="5" spans="1:5" x14ac:dyDescent="0.35">
@@ -1493,9 +1505,15 @@
       <c r="A6" s="9" t="s">
         <v>236</v>
       </c>
-      <c r="B6" s="9"/>
-      <c r="C6" s="10"/>
-      <c r="D6" s="10"/>
+      <c r="B6" s="9" t="s">
+        <v>254</v>
+      </c>
+      <c r="C6" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D6" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E6" s="11" t="s">
         <v>248</v>
       </c>
@@ -1507,8 +1525,12 @@
       <c r="B7" s="9" t="s">
         <v>244</v>
       </c>
-      <c r="C7" s="10"/>
-      <c r="D7" s="10"/>
+      <c r="C7" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D7" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E7" s="14" t="s">
         <v>245</v>
       </c>
@@ -1520,8 +1542,12 @@
       <c r="B8" s="9" t="s">
         <v>246</v>
       </c>
-      <c r="C8" s="10"/>
-      <c r="D8" s="10"/>
+      <c r="C8" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D8" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E8" s="15" t="s">
         <v>249</v>
       </c>
@@ -1533,8 +1559,12 @@
       <c r="B9" s="9" t="s">
         <v>247</v>
       </c>
-      <c r="C9" s="10"/>
-      <c r="D9" s="10"/>
+      <c r="C9" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D9" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E9" s="15" t="s">
         <v>250</v>
       </c>
@@ -1546,8 +1576,12 @@
       <c r="B10" s="9" t="s">
         <v>0</v>
       </c>
-      <c r="C10" s="10"/>
-      <c r="D10" s="10"/>
+      <c r="C10" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D10" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E10" s="15"/>
     </row>
     <row r="11" spans="1:5" x14ac:dyDescent="0.35">
@@ -1557,8 +1591,12 @@
       <c r="B11" s="9" t="s">
         <v>251</v>
       </c>
-      <c r="C11" s="15"/>
-      <c r="D11" s="10"/>
+      <c r="C11" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D11" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:5" x14ac:dyDescent="0.35">
@@ -1568,8 +1606,12 @@
       <c r="B12" s="16" t="s">
         <v>46</v>
       </c>
-      <c r="C12" s="15"/>
-      <c r="D12" s="10"/>
+      <c r="C12" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D12" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E12" s="15"/>
     </row>
     <row r="13" spans="1:5" x14ac:dyDescent="0.35">
@@ -1579,8 +1621,12 @@
       <c r="B13" s="9" t="s">
         <v>48</v>
       </c>
-      <c r="C13" s="15"/>
-      <c r="D13" s="10"/>
+      <c r="C13" s="23">
+        <v>46299</v>
+      </c>
+      <c r="D13" s="10" t="s">
+        <v>253</v>
+      </c>
       <c r="E13" s="15"/>
     </row>
     <row r="14" spans="1:5" x14ac:dyDescent="0.35">
@@ -1590,7 +1636,7 @@
       <c r="B14" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="C14" s="15"/>
+      <c r="C14" s="23"/>
       <c r="D14" s="10"/>
       <c r="E14" s="15"/>
     </row>
@@ -1601,7 +1647,7 @@
       <c r="B15" s="9" t="s">
         <v>52</v>
       </c>
-      <c r="C15" s="15"/>
+      <c r="C15" s="23"/>
       <c r="D15" s="10"/>
       <c r="E15" s="15"/>
     </row>
@@ -1628,33 +1674,33 @@
       <c r="E17" s="15"/>
     </row>
     <row r="18" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A18" s="16" t="s">
+      <c r="A18" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B18" s="16" t="s">
-        <v>58</v>
+      <c r="B18" s="9" t="s">
+        <v>60</v>
       </c>
       <c r="C18" s="15"/>
       <c r="D18" s="10"/>
       <c r="E18" s="15"/>
     </row>
     <row r="19" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A19" s="9" t="s">
+      <c r="A19" s="24" t="s">
         <v>42</v>
       </c>
       <c r="B19" s="9" t="s">
-        <v>60</v>
+        <v>62</v>
       </c>
       <c r="C19" s="15"/>
       <c r="D19" s="10"/>
       <c r="E19" s="15"/>
     </row>
     <row r="20" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A20" s="16" t="s">
+      <c r="A20" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B20" s="16" t="s">
-        <v>62</v>
+      <c r="B20" s="9" t="s">
+        <v>64</v>
       </c>
       <c r="C20" s="15"/>
       <c r="D20" s="10"/>
@@ -1665,18 +1711,18 @@
         <v>42</v>
       </c>
       <c r="B21" s="9" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
       <c r="C21" s="15"/>
       <c r="D21" s="10"/>
       <c r="E21" s="15"/>
     </row>
     <row r="22" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A22" s="16" t="s">
+      <c r="A22" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B22" s="16" t="s">
-        <v>66</v>
+      <c r="B22" s="9" t="s">
+        <v>68</v>
       </c>
       <c r="C22" s="15"/>
       <c r="D22" s="10"/>
@@ -1687,18 +1733,18 @@
         <v>42</v>
       </c>
       <c r="B23" s="9" t="s">
-        <v>68</v>
+        <v>70</v>
       </c>
       <c r="C23" s="15"/>
       <c r="D23" s="10"/>
       <c r="E23" s="15"/>
     </row>
     <row r="24" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A24" s="16" t="s">
+      <c r="A24" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B24" s="16" t="s">
-        <v>70</v>
+      <c r="B24" s="9" t="s">
+        <v>54</v>
       </c>
       <c r="C24" s="15"/>
       <c r="D24" s="10"/>
@@ -1709,18 +1755,18 @@
         <v>42</v>
       </c>
       <c r="B25" s="9" t="s">
-        <v>54</v>
+        <v>73</v>
       </c>
       <c r="C25" s="15"/>
       <c r="D25" s="10"/>
       <c r="E25" s="15"/>
     </row>
     <row r="26" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A26" s="16" t="s">
+      <c r="A26" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B26" s="16" t="s">
-        <v>73</v>
+      <c r="B26" s="9" t="s">
+        <v>75</v>
       </c>
       <c r="C26" s="15"/>
       <c r="D26" s="10"/>
@@ -1731,7 +1777,7 @@
         <v>42</v>
       </c>
       <c r="B27" s="9" t="s">
-        <v>75</v>
+        <v>77</v>
       </c>
       <c r="C27" s="15"/>
       <c r="D27" s="10"/>
@@ -1741,8 +1787,8 @@
       <c r="A28" s="16" t="s">
         <v>42</v>
       </c>
-      <c r="B28" s="16" t="s">
-        <v>77</v>
+      <c r="B28" s="9" t="s">
+        <v>79</v>
       </c>
       <c r="C28" s="15"/>
       <c r="D28" s="10"/>
@@ -1753,7 +1799,7 @@
         <v>42</v>
       </c>
       <c r="B29" s="9" t="s">
-        <v>79</v>
+        <v>81</v>
       </c>
       <c r="C29" s="15"/>
       <c r="D29" s="10"/>
@@ -1764,7 +1810,7 @@
         <v>42</v>
       </c>
       <c r="B30" s="16" t="s">
-        <v>81</v>
+        <v>83</v>
       </c>
       <c r="C30" s="15"/>
       <c r="D30" s="10"/>
@@ -1775,7 +1821,7 @@
         <v>42</v>
       </c>
       <c r="B31" s="9" t="s">
-        <v>83</v>
+        <v>85</v>
       </c>
       <c r="C31" s="15"/>
       <c r="D31" s="10"/>
@@ -1786,7 +1832,7 @@
         <v>42</v>
       </c>
       <c r="B32" s="16" t="s">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C32" s="15"/>
       <c r="D32" s="10"/>
@@ -1797,7 +1843,7 @@
         <v>42</v>
       </c>
       <c r="B33" s="9" t="s">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="C33" s="15"/>
       <c r="D33" s="10"/>
@@ -1808,7 +1854,7 @@
         <v>42</v>
       </c>
       <c r="B34" s="16" t="s">
-        <v>89</v>
+        <v>91</v>
       </c>
       <c r="C34" s="15"/>
       <c r="D34" s="10"/>
@@ -1819,18 +1865,18 @@
         <v>42</v>
       </c>
       <c r="B35" s="9" t="s">
-        <v>91</v>
+        <v>93</v>
       </c>
       <c r="C35" s="15"/>
       <c r="D35" s="10"/>
       <c r="E35" s="15"/>
     </row>
     <row r="36" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B36" s="16" t="s">
-        <v>93</v>
+      <c r="B36" s="9" t="s">
+        <v>95</v>
       </c>
       <c r="C36" s="15"/>
       <c r="D36" s="10"/>
@@ -1841,18 +1887,18 @@
         <v>42</v>
       </c>
       <c r="B37" s="9" t="s">
-        <v>95</v>
+        <v>97</v>
       </c>
       <c r="C37" s="15"/>
       <c r="D37" s="10"/>
       <c r="E37" s="15"/>
     </row>
     <row r="38" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A38" s="16" t="s">
+      <c r="A38" s="9" t="s">
         <v>42</v>
       </c>
-      <c r="B38" s="16" t="s">
-        <v>97</v>
+      <c r="B38" s="9" t="s">
+        <v>99</v>
       </c>
       <c r="C38" s="15"/>
       <c r="D38" s="10"/>
@@ -1863,18 +1909,18 @@
         <v>42</v>
       </c>
       <c r="B39" s="9" t="s">
-        <v>99</v>
+        <v>101</v>
       </c>
       <c r="C39" s="15"/>
       <c r="D39" s="10"/>
       <c r="E39" s="15"/>
     </row>
     <row r="40" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A40" s="16" t="s">
-        <v>42</v>
-      </c>
-      <c r="B40" s="16" t="s">
-        <v>101</v>
+      <c r="A40" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="B40" s="9" t="s">
+        <v>105</v>
       </c>
       <c r="C40" s="15"/>
       <c r="D40" s="10"/>
@@ -1885,7 +1931,7 @@
         <v>103</v>
       </c>
       <c r="B41" s="9" t="s">
-        <v>105</v>
+        <v>107</v>
       </c>
       <c r="C41" s="15"/>
       <c r="D41" s="10"/>
@@ -1896,7 +1942,7 @@
         <v>103</v>
       </c>
       <c r="B42" s="9" t="s">
-        <v>107</v>
+        <v>109</v>
       </c>
       <c r="C42" s="15"/>
       <c r="D42" s="10"/>
@@ -1907,7 +1953,7 @@
         <v>103</v>
       </c>
       <c r="B43" s="9" t="s">
-        <v>109</v>
+        <v>111</v>
       </c>
       <c r="C43" s="15"/>
       <c r="D43" s="10"/>
@@ -1918,7 +1964,7 @@
         <v>103</v>
       </c>
       <c r="B44" s="9" t="s">
-        <v>111</v>
+        <v>113</v>
       </c>
       <c r="C44" s="15"/>
       <c r="D44" s="10"/>
@@ -1929,7 +1975,7 @@
         <v>103</v>
       </c>
       <c r="B45" s="9" t="s">
-        <v>113</v>
+        <v>115</v>
       </c>
       <c r="C45" s="15"/>
       <c r="D45" s="10"/>
@@ -1940,7 +1986,7 @@
         <v>103</v>
       </c>
       <c r="B46" s="9" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C46" s="15"/>
       <c r="D46" s="10"/>
@@ -1951,7 +1997,7 @@
         <v>103</v>
       </c>
       <c r="B47" s="9" t="s">
-        <v>117</v>
+        <v>119</v>
       </c>
       <c r="C47" s="15"/>
       <c r="D47" s="10"/>
@@ -1962,7 +2008,7 @@
         <v>103</v>
       </c>
       <c r="B48" s="9" t="s">
-        <v>119</v>
+        <v>121</v>
       </c>
       <c r="C48" s="15"/>
       <c r="D48" s="10"/>
@@ -1973,7 +2019,7 @@
         <v>103</v>
       </c>
       <c r="B49" s="9" t="s">
-        <v>121</v>
+        <v>123</v>
       </c>
       <c r="C49" s="15"/>
       <c r="D49" s="10"/>
@@ -1984,7 +2030,7 @@
         <v>103</v>
       </c>
       <c r="B50" s="9" t="s">
-        <v>123</v>
+        <v>125</v>
       </c>
       <c r="C50" s="15"/>
       <c r="D50" s="10"/>
@@ -1995,7 +2041,7 @@
         <v>103</v>
       </c>
       <c r="B51" s="9" t="s">
-        <v>125</v>
+        <v>127</v>
       </c>
       <c r="C51" s="15"/>
       <c r="D51" s="10"/>
@@ -2006,7 +2052,7 @@
         <v>103</v>
       </c>
       <c r="B52" s="9" t="s">
-        <v>127</v>
+        <v>129</v>
       </c>
       <c r="C52" s="15"/>
       <c r="D52" s="10"/>
@@ -2017,7 +2063,7 @@
         <v>103</v>
       </c>
       <c r="B53" s="9" t="s">
-        <v>129</v>
+        <v>131</v>
       </c>
       <c r="C53" s="15"/>
       <c r="D53" s="10"/>
@@ -2028,7 +2074,7 @@
         <v>103</v>
       </c>
       <c r="B54" s="9" t="s">
-        <v>131</v>
+        <v>133</v>
       </c>
       <c r="C54" s="15"/>
       <c r="D54" s="10"/>
@@ -2039,7 +2085,7 @@
         <v>103</v>
       </c>
       <c r="B55" s="9" t="s">
-        <v>133</v>
+        <v>135</v>
       </c>
       <c r="C55" s="15"/>
       <c r="D55" s="10"/>
@@ -2050,7 +2096,7 @@
         <v>103</v>
       </c>
       <c r="B56" s="9" t="s">
-        <v>135</v>
+        <v>137</v>
       </c>
       <c r="C56" s="15"/>
       <c r="D56" s="10"/>
@@ -2061,7 +2107,7 @@
         <v>103</v>
       </c>
       <c r="B57" s="9" t="s">
-        <v>137</v>
+        <v>139</v>
       </c>
       <c r="C57" s="15"/>
       <c r="D57" s="10"/>
@@ -2072,7 +2118,7 @@
         <v>103</v>
       </c>
       <c r="B58" s="9" t="s">
-        <v>139</v>
+        <v>141</v>
       </c>
       <c r="C58" s="15"/>
       <c r="D58" s="10"/>
@@ -2083,7 +2129,7 @@
         <v>103</v>
       </c>
       <c r="B59" s="9" t="s">
-        <v>141</v>
+        <v>143</v>
       </c>
       <c r="C59" s="15"/>
       <c r="D59" s="10"/>
@@ -2091,10 +2137,10 @@
     </row>
     <row r="60" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A60" s="9" t="s">
-        <v>103</v>
+        <v>145</v>
       </c>
       <c r="B60" s="9" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="C60" s="15"/>
       <c r="D60" s="10"/>
@@ -2105,7 +2151,7 @@
         <v>145</v>
       </c>
       <c r="B61" s="9" t="s">
-        <v>147</v>
+        <v>149</v>
       </c>
       <c r="C61" s="15"/>
       <c r="D61" s="10"/>
@@ -2116,7 +2162,7 @@
         <v>145</v>
       </c>
       <c r="B62" s="9" t="s">
-        <v>149</v>
+        <v>151</v>
       </c>
       <c r="C62" s="15"/>
       <c r="D62" s="10"/>
@@ -2127,7 +2173,7 @@
         <v>145</v>
       </c>
       <c r="B63" s="9" t="s">
-        <v>151</v>
+        <v>153</v>
       </c>
       <c r="C63" s="15"/>
       <c r="D63" s="10"/>
@@ -2138,7 +2184,7 @@
         <v>145</v>
       </c>
       <c r="B64" s="9" t="s">
-        <v>153</v>
+        <v>155</v>
       </c>
       <c r="C64" s="15"/>
       <c r="D64" s="10"/>
@@ -2149,18 +2195,18 @@
         <v>145</v>
       </c>
       <c r="B65" s="9" t="s">
-        <v>155</v>
+        <v>157</v>
       </c>
       <c r="C65" s="15"/>
       <c r="D65" s="10"/>
       <c r="E65" s="15"/>
     </row>
     <row r="66" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A66" s="9" t="s">
-        <v>145</v>
+      <c r="A66" s="15" t="s">
+        <v>159</v>
       </c>
       <c r="B66" s="9" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="C66" s="15"/>
       <c r="D66" s="10"/>
@@ -2171,10 +2217,10 @@
         <v>159</v>
       </c>
       <c r="B67" s="9" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="C67" s="15"/>
-      <c r="D67" s="10"/>
+      <c r="D67" s="15"/>
       <c r="E67" s="15"/>
     </row>
     <row r="68" spans="1:5" x14ac:dyDescent="0.35">
@@ -2182,7 +2228,7 @@
         <v>159</v>
       </c>
       <c r="B68" s="9" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="C68" s="15"/>
       <c r="D68" s="15"/>
@@ -2193,95 +2239,95 @@
         <v>159</v>
       </c>
       <c r="B69" s="9" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="C69" s="15"/>
       <c r="D69" s="15"/>
       <c r="E69" s="15"/>
     </row>
     <row r="70" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A70" s="15" t="s">
+      <c r="A70" s="9" t="s">
         <v>159</v>
       </c>
       <c r="B70" s="9" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="C70" s="15"/>
       <c r="D70" s="15"/>
       <c r="E70" s="15"/>
     </row>
     <row r="71" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A71" s="15" t="s">
+      <c r="A71" s="9" t="s">
         <v>159</v>
       </c>
       <c r="B71" s="9" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C71" s="15"/>
       <c r="D71" s="15"/>
       <c r="E71" s="15"/>
     </row>
     <row r="72" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A72" s="15" t="s">
-        <v>159</v>
+      <c r="A72" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B72" s="9" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="C72" s="15"/>
       <c r="D72" s="15"/>
       <c r="E72" s="15"/>
     </row>
     <row r="73" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A73" s="15" t="s">
-        <v>159</v>
+      <c r="A73" s="9" t="s">
+        <v>175</v>
       </c>
       <c r="B73" s="9" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="C73" s="15"/>
       <c r="D73" s="15"/>
       <c r="E73" s="15"/>
     </row>
     <row r="74" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A74" s="15" t="s">
+      <c r="A74" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B74" s="17" t="s">
-        <v>177</v>
+      <c r="B74" s="9" t="s">
+        <v>183</v>
       </c>
       <c r="C74" s="15"/>
       <c r="D74" s="15"/>
       <c r="E74" s="15"/>
     </row>
     <row r="75" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A75" s="15" t="s">
+      <c r="A75" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B75" s="15" t="s">
-        <v>179</v>
+      <c r="B75" s="9" t="s">
+        <v>185</v>
       </c>
       <c r="C75" s="15"/>
       <c r="D75" s="15"/>
       <c r="E75" s="15"/>
     </row>
     <row r="76" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A76" s="15" t="s">
+      <c r="A76" s="9" t="s">
         <v>175</v>
       </c>
-      <c r="B76" s="17" t="s">
-        <v>181</v>
+      <c r="B76" s="9" t="s">
+        <v>187</v>
       </c>
       <c r="C76" s="15"/>
       <c r="D76" s="15"/>
       <c r="E76" s="15"/>
     </row>
     <row r="77" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A77" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B77" s="15" t="s">
-        <v>183</v>
+      <c r="A77" s="9" t="s">
+        <v>191</v>
+      </c>
+      <c r="B77" s="9" t="s">
+        <v>193</v>
       </c>
       <c r="C77" s="15"/>
       <c r="D77" s="15"/>
@@ -2289,10 +2335,10 @@
     </row>
     <row r="78" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A78" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B78" s="17" t="s">
-        <v>185</v>
+        <v>191</v>
+      </c>
+      <c r="B78" s="9" t="s">
+        <v>195</v>
       </c>
       <c r="C78" s="15"/>
       <c r="D78" s="15"/>
@@ -2300,10 +2346,10 @@
     </row>
     <row r="79" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A79" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B79" s="15" t="s">
-        <v>187</v>
+        <v>191</v>
+      </c>
+      <c r="B79" s="9" t="s">
+        <v>197</v>
       </c>
       <c r="C79" s="15"/>
       <c r="D79" s="15"/>
@@ -2311,10 +2357,10 @@
     </row>
     <row r="80" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A80" s="15" t="s">
-        <v>175</v>
-      </c>
-      <c r="B80" s="17" t="s">
-        <v>189</v>
+        <v>191</v>
+      </c>
+      <c r="B80" s="9" t="s">
+        <v>199</v>
       </c>
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
@@ -2325,7 +2371,7 @@
         <v>191</v>
       </c>
       <c r="B81" s="9" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="C81" s="15"/>
       <c r="D81" s="15"/>
@@ -2336,7 +2382,7 @@
         <v>191</v>
       </c>
       <c r="B82" s="9" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="C82" s="15"/>
       <c r="D82" s="15"/>
@@ -2347,7 +2393,7 @@
         <v>191</v>
       </c>
       <c r="B83" s="9" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="C83" s="15"/>
       <c r="D83" s="15"/>
@@ -2358,7 +2404,7 @@
         <v>191</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="C84" s="15"/>
       <c r="D84" s="15"/>
@@ -2369,51 +2415,51 @@
         <v>191</v>
       </c>
       <c r="B85" s="9" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C85" s="15"/>
       <c r="D85" s="15"/>
       <c r="E85" s="15"/>
     </row>
     <row r="86" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A86" s="15" t="s">
-        <v>191</v>
+      <c r="A86" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B86" s="9" t="s">
-        <v>203</v>
+        <v>213</v>
       </c>
       <c r="C86" s="15"/>
       <c r="D86" s="15"/>
       <c r="E86" s="15"/>
     </row>
     <row r="87" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A87" s="15" t="s">
-        <v>191</v>
+      <c r="A87" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B87" s="9" t="s">
-        <v>205</v>
+        <v>215</v>
       </c>
       <c r="C87" s="15"/>
       <c r="D87" s="15"/>
       <c r="E87" s="15"/>
     </row>
     <row r="88" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A88" s="15" t="s">
-        <v>191</v>
+      <c r="A88" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B88" s="9" t="s">
-        <v>207</v>
+        <v>217</v>
       </c>
       <c r="C88" s="15"/>
       <c r="D88" s="15"/>
       <c r="E88" s="15"/>
     </row>
     <row r="89" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A89" s="15" t="s">
-        <v>191</v>
+      <c r="A89" s="9" t="s">
+        <v>211</v>
       </c>
       <c r="B89" s="9" t="s">
-        <v>209</v>
+        <v>219</v>
       </c>
       <c r="C89" s="15"/>
       <c r="D89" s="15"/>
@@ -2424,7 +2470,7 @@
         <v>211</v>
       </c>
       <c r="B90" s="9" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="C90" s="15"/>
       <c r="D90" s="15"/>
@@ -2435,7 +2481,7 @@
         <v>211</v>
       </c>
       <c r="B91" s="9" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="C91" s="15"/>
       <c r="D91" s="15"/>
@@ -2446,7 +2492,7 @@
         <v>211</v>
       </c>
       <c r="B92" s="9" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="C92" s="15"/>
       <c r="D92" s="15"/>
@@ -2454,10 +2500,10 @@
     </row>
     <row r="93" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A93" s="9" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B93" s="9" t="s">
-        <v>219</v>
+        <v>229</v>
       </c>
       <c r="C93" s="15"/>
       <c r="D93" s="15"/>
@@ -2465,58 +2511,14 @@
     </row>
     <row r="94" spans="1:5" x14ac:dyDescent="0.35">
       <c r="A94" s="9" t="s">
-        <v>211</v>
+        <v>227</v>
       </c>
       <c r="B94" s="9" t="s">
-        <v>221</v>
+        <v>231</v>
       </c>
       <c r="C94" s="15"/>
       <c r="D94" s="15"/>
       <c r="E94" s="15"/>
-    </row>
-    <row r="95" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A95" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B95" s="9" t="s">
-        <v>223</v>
-      </c>
-      <c r="C95" s="15"/>
-      <c r="D95" s="15"/>
-      <c r="E95" s="15"/>
-    </row>
-    <row r="96" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A96" s="9" t="s">
-        <v>211</v>
-      </c>
-      <c r="B96" s="9" t="s">
-        <v>225</v>
-      </c>
-      <c r="C96" s="15"/>
-      <c r="D96" s="15"/>
-      <c r="E96" s="15"/>
-    </row>
-    <row r="97" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A97" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="B97" s="9" t="s">
-        <v>229</v>
-      </c>
-      <c r="C97" s="15"/>
-      <c r="D97" s="15"/>
-      <c r="E97" s="15"/>
-    </row>
-    <row r="98" spans="1:5" x14ac:dyDescent="0.35">
-      <c r="A98" s="9" t="s">
-        <v>227</v>
-      </c>
-      <c r="B98" s="9" t="s">
-        <v>231</v>
-      </c>
-      <c r="C98" s="15"/>
-      <c r="D98" s="15"/>
-      <c r="E98" s="15"/>
     </row>
   </sheetData>
   <mergeCells count="2">
@@ -2539,7 +2541,7 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D98" xr:uid="{7882E07B-F4AF-4E54-8EB1-9A648D8FCC6B}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="D4:D94" xr:uid="{7882E07B-F4AF-4E54-8EB1-9A648D8FCC6B}">
       <formula1>"Wykonano"</formula1>
     </dataValidation>
   </dataValidations>
